--- a/main/ig/CodeSystem-cs-fr-v2-0066.xlsx
+++ b/main/ig/CodeSystem-cs-fr-v2-0066.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:18:46+00:00</t>
+    <t>2026-05-05T15:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
